--- a/02_加值成品/九下/九下2-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/九下/九下2-2_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三下學期 九下2-2 電流的磁效應　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國三下學期 九下2-2 電流的磁效應　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>電流通過導線周圍會產生？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>有磁性</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>對調</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>磁場環繞方向</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>磁場</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>磁效應</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>電流的磁效應由誰發現？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>厄斯特</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>消失</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>同心圓</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>安培右手定則</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>發現</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>判斷電流磁場方向用？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>鐵芯</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>對調</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>磁場</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>安培右手定則</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>定則</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>線圈通電形成？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>反轉</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>對調</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>電磁鐵</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>同心圓</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>磁性</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>電磁鐵斷電磁性會？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>鐵芯</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>安培右手定則</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>有磁性</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>消失</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>可控</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>增加電磁鐵磁性可加？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>安培右手定則</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>鐵芯</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>對調</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>增強</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="34" customHeight="1">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>增強</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>直導線周圍磁場成？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>電磁鐵</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>增強</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>同心圓</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>鐵芯</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>形狀</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>電磁鐵通電時？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>電磁鐵</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>磁場</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>磁性可控制</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>有磁性</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>產磁</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>通電導線周圍會產生什麼？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>厄斯特</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>電磁鐵</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>磁場</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>磁效應</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>線圈通電並加鐵芯做成？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>磁性可控制</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>安培右手定則</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>磁極對調</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>電磁鐵</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>磁性</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三下學期 九下2-2 電流的磁效應　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國三下學期 九下2-2 電流的磁效應　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>右手定則大拇指指？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>磁場</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>同心圓</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>電流方向</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>安培右手定則</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>拇指</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>右手定則四指表示？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>同心圓</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>消失</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>電磁鐵</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>磁場環繞方向</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>四指</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>增加線圈匝數磁性？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>增強</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>同心圓</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>對調</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>電磁鐵</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>匝數</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>增大電流磁性？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>增強</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>磁場環繞方向</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>厄斯特</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>同心圓</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>電流</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>電磁鐵優於永久磁鐵在？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>對調</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>磁性可控制</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>磁場</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>消失</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>可調</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>電流方向反轉磁場方向？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>反轉</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>磁性可控制</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>磁場環繞方向</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>厄斯特</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>隨電流</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>電磁起重機利用？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>安培右手定則</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>磁場</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>磁性可控制</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>電磁鐵</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>吸鐵</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>斷電後電磁鐵能吸鐵嗎？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>反轉</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>增強</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>對調</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>不能</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>無磁</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>電磁鐵斷電後磁性會？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>對調</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>電磁鐵</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>磁場環繞方向</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>消失</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>可控</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>要增強電磁鐵磁性可增加？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>拇指指電流四指繞出磁場方向</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>通電產磁吸附、斷電釋放</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>加鐵芯、增加匝數、增大電流</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>線圈匝數或電流</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>增強</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三下學期 九下2-2 電流的磁效應　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國三下學期 九下2-2 電流的磁效應　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>如何增強電磁鐵的磁性(三法)？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>加鐵芯、增加匝數、增大電流</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>鐵芯被磁化增強磁場</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>磁性可開關與調整</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>通電產磁吸附、斷電釋放</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>增強</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>電磁鐵相較永久磁鐵的優勢？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>線圈匝數或電流</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>拇指指電流四指繞出磁場方向</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>通電產磁吸附、斷電釋放</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>磁性可開關與調整</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>可控</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>用右手定則判斷通電直導線周圍磁場？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>電流能產生磁場,電磁相關</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>加鐵芯、增加匝數、增大電流</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>拇指指電流四指繞出磁場方向</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>磁性可開關與調整</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>定則</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>電磁起重機為何能吸放廢鐵？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>拇指指電流四指繞出磁場方向</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>鐵芯被磁化增強磁場</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>電流能產生磁場,電磁相關</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>通電產磁吸附、斷電釋放</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>應用</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>厄斯特實驗說明電與磁的關係？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>電流能產生磁場,電磁相關</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>通電產磁吸附、斷電釋放</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>鐵芯被磁化增強磁場</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>磁性可開關與調整</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>關聯</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>改變電流方向對電磁鐵極性影響？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>增強</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>安培右手定則</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>磁極對調</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>反轉</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>方向</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>電鈴如何利用電磁鐵反覆敲響？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>通電吸動斷電釋放反覆</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>鐵芯被磁化增強磁場</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>通電產磁吸附、斷電釋放</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>加鐵芯、增加匝數、增大電流</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>機制</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>線圈中放入鐵芯磁性大增原因？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>磁性可開關與調整</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>鐵芯被磁化增強磁場</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>通電產磁吸附、斷電釋放</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>通電吸動斷電釋放反覆</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>鐵芯</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>電磁鐵比永久磁鐵方便在哪？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>拇指指電流四指繞出磁場方向</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>磁性可開關與調整</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>鐵芯被磁化增強磁場</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>通電吸動斷電釋放反覆</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>可控</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>電流方向反轉電磁鐵的磁極會？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>對調</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>厄斯特</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>磁極對調</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>電流方向</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>方向</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/九下/九下2-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/九下/九下2-2_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>磁效應</t>
+          <t>磁效應：電流流過導線時，導線周圍空間會出現磁場，這就是電流的磁效應</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>發現</t>
+          <t>發現：科學家厄斯特最早發現通電導線旁的指南針會偏轉，證實電流會產生磁場</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>定則</t>
+          <t>定則：要判斷電流產生的磁場方向，可以用安培右手定則來幫忙判斷</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>磁性</t>
+          <t>磁性：把導線繞成線圈再通電，就會形成具有磁性的電磁鐵</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>可控</t>
+          <t>可控：電磁鐵的磁性是靠電流產生的，一旦切斷電源磁性就會立刻消失</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>增強</t>
+          <t>增強：在線圈中間插入鐵芯，可以讓磁場集中變強，增強電磁鐵的磁性</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>形狀</t>
+          <t>形狀：通電的直導線周圍所產生的磁場，會呈現一圈圈的同心圓形狀</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>產磁</t>
+          <t>產磁：只要線圈持續通電，電磁鐵就會一直保持磁性，能夠吸引鐵製物品</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>磁效應</t>
+          <t>磁效應：電流通過導線時，周圍空間會出現磁場，這是電流的磁效應</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>磁性</t>
+          <t>磁性：線圈通電並在中間放入鐵芯，可以做成磁性更強的電磁鐵</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>拇指</t>
+          <t>拇指：使用安培右手定則時，大拇指指的方向代表電流流動的方向</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>四指</t>
+          <t>四指：右手四指彎曲的方向，代表電流所產生的磁場環繞導線的方向</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>匝數</t>
+          <t>匝數：線圈繞的圈數越多，產生的磁場就會疊加得越強，磁性也越強</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>電流</t>
+          <t>電流：通過線圈的電流越大，所產生的磁場也會跟著變強</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>可調</t>
+          <t>可調：電磁鐵可以靠通電、斷電來開關磁性，也能調整電流大小改變強弱，比永久磁鐵靈活</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>隨電流</t>
+          <t>隨電流：電流的方向若反過來，所產生的磁場方向也會跟著反轉</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>吸鐵</t>
+          <t>吸鐵：電磁起重機是利用強力電磁鐵通電後產生磁性，用來吸起大量廢鐵</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>無磁</t>
+          <t>無磁：一旦切斷電源，電磁鐵就失去磁性，沒有辦法再吸住鐵製物品</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>可控</t>
+          <t>可控：電磁鐵的磁性靠電流維持，一旦斷電磁性就會立刻消失</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>增強</t>
+          <t>增強：增加線圈繞的圈數，或加大通過的電流，都能讓電磁鐵磁性變強</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>增強</t>
+          <t>增強：可以在線圈中加入鐵芯、增加線圈繞的圈數，或是加大通過的電流，三種方法都能增強電磁鐵的磁性</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>可控</t>
+          <t>可控：電磁鐵能靠通電斷電來開關磁性，還能調整電流大小控制磁性強弱，這是永久磁鐵做不到的</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>定則</t>
+          <t>定則：把右手拇指指向電流流動的方向，其餘四指自然彎曲的方向，就是磁場環繞導線的方向</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>應用</t>
+          <t>應用：通電時電磁鐵產生磁性把廢鐵吸住搬運，需要放下時只要切斷電源，磁性消失廢鐵就會掉落</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>關聯</t>
+          <t>關聯：厄斯特的實驗證明了電流會在周圍空間產生磁場，說明電和磁其實是彼此相關的現象</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>方向</t>
+          <t>方向：把通入電磁鐵線圈的電流方向反過來，電磁鐵原本的N極和S極位置也會跟著對調</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>機制</t>
+          <t>機制：電鈴利用電磁鐵通電時吸動槌子敲鐘，斷電時槌子彈回又自動接通電路，如此反覆動作發出聲響</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>鐵芯</t>
+          <t>鐵芯：鐵芯放入線圈中會被線圈的磁場磁化，本身也產生磁性，兩者磁場疊加使整體磁性大幅增強</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>可控</t>
+          <t>可控：電磁鐵能靠通電斷電開關磁性，也能調整電流大小改變強弱，比永久磁鐵更靈活</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>方向</t>
+          <t>方向：把通入線圈的電流方向反過來，電磁鐵原本的N極和S極位置也會跟著對調</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/九下/九下2-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/九下/九下2-2_三種難度測驗卷.xlsx
@@ -563,17 +563,17 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>有磁性</t>
+          <t>安培右手定則</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>對調</t>
+          <t>磁性可控制</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>磁場環繞方向</t>
+          <t>消失</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -883,17 +883,17 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>不能</t>
+          <t>消失</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>厄斯特</t>
+          <t>增強</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>電磁鐵</t>
+          <t>安培右手定則</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -1079,17 +1079,17 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>同心圓</t>
+          <t>鐵芯</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>消失</t>
+          <t>電磁鐵</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>電磁鐵</t>
+          <t>磁性可控制</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>增強</t>
+          <t>有磁性</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>安培右手定則</t>
+          <t>消失</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>反轉</t>
+          <t>鐵芯</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -1880,17 +1880,17 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>厄斯特</t>
+          <t>反轉</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>磁極對調</t>
+          <t>同心圓</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>電流方向</t>
+          <t>安培右手定則</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
